--- a/sample/input.xlsx
+++ b/sample/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,145 +441,160 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Oak</t>
+          <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30026196226</t>
+          <t>30023084091</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Walnut</t>
+          <t>18 Oak 340x777 CAD-230840</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30031847710</t>
+          <t>30034453168</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x1200 Oak</t>
+          <t>18 Oak 431x661 CAD-344531</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30031847711</t>
+          <t>30040995108</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x1200 Walnut</t>
+          <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30044982033</t>
+          <t>30031976178</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tiled Panel 300x600 Oak</t>
+          <t>18 Wte 461x999 CAD-319761</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30055310884</t>
+          <t>30030896419</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tiled Panel 900x900 Grey Stone</t>
+          <t>18 Wte 464x972 CAD-308964</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30055310885</t>
+          <t>30061891516</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tiled Panel 900x900 White Stone</t>
+          <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30066471192</t>
+          <t>30060494285</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 Grey Stone</t>
+          <t>18 Anth 442x912 CAD-604942</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30066471193</t>
+          <t>30052872586</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tiled Panel 600x600 White Stone</t>
+          <t>18 Oak 625x721 CAD-528725</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>30067353897</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18 Oak 638x683 CAD-673538</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>30099999999</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tiled Panel 1200x1200 Oak (new line)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tiled Panel (unknown SKU test row)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
     </row>

--- a/sample/input.xlsx
+++ b/sample/input.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
